--- a/afd/msr.xlsx
+++ b/afd/msr.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B690CA9-B8D2-2E4A-9163-C0B9C72F5C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59117A7-ED16-C940-B445-F2184322C1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,14 +11,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$58</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="188">
   <si>
     <t xml:space="preserve">Code </t>
   </si>
@@ -522,13 +522,73 @@
   </si>
   <si>
     <t>Mrs. Rimpa Sardar</t>
+  </si>
+  <si>
+    <t>ADITYA AGENCIES</t>
+  </si>
+  <si>
+    <t>HARI OM ENTERPRISES</t>
+  </si>
+  <si>
+    <t>MUZAFFARPUR</t>
+  </si>
+  <si>
+    <t>HAJIPUR</t>
+  </si>
+  <si>
+    <t>MALIK MEDICAL AGENCIES</t>
+  </si>
+  <si>
+    <t>RANCHI</t>
+  </si>
+  <si>
+    <t>NAMAN DISTRIBUTORS</t>
+  </si>
+  <si>
+    <t>RAMPURHAT</t>
+  </si>
+  <si>
+    <t>PAUL ENTERPRISE</t>
+  </si>
+  <si>
+    <t>NADIA</t>
+  </si>
+  <si>
+    <t>RIDDHI SIDDHI</t>
+  </si>
+  <si>
+    <t>SURYA ENTERPRISES</t>
+  </si>
+  <si>
+    <t>NAWADA</t>
+  </si>
+  <si>
+    <t>Mr. Deepak Kumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC144 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC082 </t>
+  </si>
+  <si>
+    <t>HPC142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC001  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC116 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC141 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,6 +624,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -967,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="21" customWidth="1"/>
@@ -2329,22 +2395,191 @@
       <c r="J51" s="10"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" s="20"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="14"/>
+      <c r="A52" s="19">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="16"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="J52" s="10"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" s="19">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" s="16"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="J53" s="10"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" s="19">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F54" s="16"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="J54" s="10"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55" s="19">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="J55" s="10"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A56" s="19">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="J56" s="10"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57" s="19">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F57" s="16"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="J57" s="10"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" s="19">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="J58" s="10"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" s="20"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J51" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J58" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:J50">
     <sortCondition ref="I25:I50"/>
   </sortState>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/afd/msr.xlsx
+++ b/afd/msr.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59117A7-ED16-C940-B445-F2184322C1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BF4351-4A94-154B-9599-93326340C25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="188">
   <si>
     <t xml:space="preserve">Code </t>
   </si>
@@ -2410,7 +2410,9 @@
       <c r="E52" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F52" s="16"/>
+      <c r="F52" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
       <c r="I52" s="16" t="s">
@@ -2434,7 +2436,9 @@
       <c r="E53" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F53" s="16"/>
+      <c r="F53" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
       <c r="I53" s="16" t="s">
@@ -2458,7 +2462,9 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="16"/>
+      <c r="F54" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
       <c r="I54" s="16" t="s">
@@ -2482,7 +2488,9 @@
       <c r="E55" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F55" s="10"/>
+      <c r="F55" s="10" t="s">
+        <v>143</v>
+      </c>
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
       <c r="I55" s="10" t="s">
@@ -2506,7 +2514,9 @@
       <c r="E56" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F56" s="10"/>
+      <c r="F56" s="10" t="s">
+        <v>143</v>
+      </c>
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
       <c r="I56" s="10" t="s">
@@ -2530,7 +2540,9 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="16"/>
+      <c r="F57" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="G57" s="10"/>
       <c r="H57" s="10"/>
       <c r="I57" s="16" t="s">
@@ -2554,7 +2566,9 @@
       <c r="E58" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F58" s="10"/>
+      <c r="F58" s="10" t="s">
+        <v>181</v>
+      </c>
       <c r="G58" s="10"/>
       <c r="H58" s="10"/>
       <c r="I58" s="10" t="s">

--- a/afd/msr.xlsx
+++ b/afd/msr.xlsx
@@ -3,22 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BF4351-4A94-154B-9599-93326340C25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2631D1F6-61CE-C644-A65C-236B02DCC32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$62</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="197">
   <si>
     <t xml:space="preserve">Code </t>
   </si>
@@ -582,6 +582,33 @@
   </si>
   <si>
     <t xml:space="preserve">HPC141 </t>
+  </si>
+  <si>
+    <t>MONORAMA MEDICAL HALL</t>
+  </si>
+  <si>
+    <t>M/S. HANSA ENTERPRISE</t>
+  </si>
+  <si>
+    <t>M.A. ASSOCIATES</t>
+  </si>
+  <si>
+    <t>M. S. ENTERPRISE</t>
+  </si>
+  <si>
+    <t>NABADWIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC120 </t>
+  </si>
+  <si>
+    <t>MONORAM</t>
+  </si>
+  <si>
+    <t>HC020</t>
+  </si>
+  <si>
+    <t>HPC106</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="21" customWidth="1"/>
@@ -2477,24 +2504,24 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>175</v>
+        <v>35</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>143</v>
+      <c r="F55" s="16" t="s">
+        <v>156</v>
       </c>
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
-      <c r="I55" s="10" t="s">
-        <v>143</v>
+      <c r="I55" s="16" t="s">
+        <v>142</v>
       </c>
       <c r="J55" s="10"/>
     </row>
@@ -2503,23 +2530,23 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F56" s="10" t="s">
+      <c r="F56" s="16" t="s">
         <v>143</v>
       </c>
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
-      <c r="I56" s="10" t="s">
+      <c r="I56" s="16" t="s">
         <v>143</v>
       </c>
       <c r="J56" s="10"/>
@@ -2528,25 +2555,25 @@
       <c r="A57" s="19">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>186</v>
+      <c r="B57" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G57" s="10"/>
       <c r="H57" s="10"/>
       <c r="I57" s="16" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J57" s="10"/>
     </row>
@@ -2555,41 +2582,145 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>181</v>
+        <v>7</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>142</v>
       </c>
       <c r="G58" s="10"/>
       <c r="H58" s="10"/>
-      <c r="I58" s="10" t="s">
+      <c r="I58" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="J58" s="10"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" s="19">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="J59" s="10"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60" s="19">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="J60" s="10"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A61" s="19">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="J61" s="10"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62" s="19">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="J58" s="10"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" s="20"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="14"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="J62" s="10"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A63" s="20"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J58" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J62" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:J50">
     <sortCondition ref="I25:I50"/>
   </sortState>
